--- a/results/04_final_refined_daily_hydroclimate_data/209/Daily_temperature_and_precipitation_station_209.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Daily_temperature_and_precipitation_station_209.xlsx
@@ -526,7 +526,7 @@
         <v>30</v>
       </c>
       <c r="J2">
-        <v>27.2</v>
+        <v>27.7</v>
       </c>
       <c r="K2">
         <v>15.4</v>
@@ -534,6 +534,9 @@
       <c r="L2">
         <v>22.4</v>
       </c>
+      <c r="M2">
+        <v>24</v>
+      </c>
       <c r="R2" s="2">
         <v>25112</v>
       </c>
@@ -555,22 +558,28 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="E3">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="F3">
         <v>21.5</v>
       </c>
+      <c r="H3">
+        <v>19.1</v>
+      </c>
       <c r="I3">
         <v>20.5</v>
       </c>
       <c r="J3">
         <v>27.7</v>
       </c>
+      <c r="K3">
+        <v>18</v>
+      </c>
       <c r="L3">
-        <v>19.1</v>
+        <v>18.4</v>
       </c>
       <c r="M3">
         <v>22.7</v>
@@ -617,7 +626,7 @@
         <v>18.4</v>
       </c>
       <c r="L4">
-        <v>23.9</v>
+        <v>21.7</v>
       </c>
       <c r="M4">
         <v>18.1</v>
@@ -651,14 +660,23 @@
       <c r="F5">
         <v>25</v>
       </c>
+      <c r="H5">
+        <v>17.3</v>
+      </c>
       <c r="I5">
         <v>31.9</v>
       </c>
       <c r="J5">
-        <v>27.6</v>
+        <v>26.2</v>
+      </c>
+      <c r="K5">
+        <v>16</v>
       </c>
       <c r="L5">
-        <v>20.8</v>
+        <v>23.9</v>
+      </c>
+      <c r="M5">
+        <v>22</v>
       </c>
       <c r="R5" s="2">
         <v>25115</v>
@@ -689,14 +707,23 @@
       <c r="F6">
         <v>26.2</v>
       </c>
+      <c r="H6">
+        <v>20</v>
+      </c>
       <c r="I6">
         <v>26.6</v>
       </c>
       <c r="J6">
         <v>24</v>
       </c>
+      <c r="K6">
+        <v>18.6</v>
+      </c>
       <c r="L6">
-        <v>26</v>
+        <v>25.8</v>
+      </c>
+      <c r="M6">
+        <v>22.8</v>
       </c>
       <c r="R6" s="2">
         <v>25116</v>
@@ -727,14 +754,23 @@
       <c r="F7">
         <v>24.3</v>
       </c>
+      <c r="H7">
+        <v>20.1</v>
+      </c>
       <c r="I7">
         <v>27.9</v>
       </c>
       <c r="J7">
-        <v>25.5</v>
+        <v>25</v>
+      </c>
+      <c r="K7">
+        <v>18.1</v>
+      </c>
+      <c r="L7">
+        <v>25.8</v>
       </c>
       <c r="M7">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="R7" s="2">
         <v>25117</v>
@@ -765,6 +801,9 @@
       <c r="F8">
         <v>23.9</v>
       </c>
+      <c r="H8">
+        <v>20.6</v>
+      </c>
       <c r="I8">
         <v>27.2</v>
       </c>
@@ -806,6 +845,9 @@
       <c r="F9">
         <v>25.5</v>
       </c>
+      <c r="H9">
+        <v>20</v>
+      </c>
       <c r="I9">
         <v>28.6</v>
       </c>
@@ -816,7 +858,7 @@
         <v>25.5</v>
       </c>
       <c r="M9">
-        <v>23.5</v>
+        <v>23.8</v>
       </c>
       <c r="R9" s="2">
         <v>25119</v>
@@ -847,12 +889,18 @@
       <c r="F10">
         <v>26.1</v>
       </c>
+      <c r="H10">
+        <v>19.8</v>
+      </c>
       <c r="I10">
         <v>30.6</v>
       </c>
       <c r="J10">
         <v>21.9</v>
       </c>
+      <c r="K10">
+        <v>18.1</v>
+      </c>
       <c r="L10">
         <v>19.2</v>
       </c>
@@ -883,19 +931,25 @@
         <v>29.5</v>
       </c>
       <c r="E11">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F11">
         <v>24.9</v>
       </c>
+      <c r="H11">
+        <v>20.4</v>
+      </c>
       <c r="I11">
         <v>28.5</v>
       </c>
       <c r="J11">
         <v>24.5</v>
       </c>
+      <c r="L11">
+        <v>21</v>
+      </c>
       <c r="M11">
-        <v>19.7</v>
+        <v>21.1</v>
       </c>
       <c r="R11" s="2">
         <v>25121</v>
@@ -917,14 +971,29 @@
       <c r="C12">
         <v>11</v>
       </c>
+      <c r="D12">
+        <v>30.8</v>
+      </c>
+      <c r="E12">
+        <v>19</v>
+      </c>
+      <c r="F12">
+        <v>24.9</v>
+      </c>
       <c r="H12">
-        <v>19.6</v>
+        <v>19.2</v>
+      </c>
+      <c r="I12">
+        <v>28.6</v>
       </c>
       <c r="J12">
         <v>26</v>
       </c>
       <c r="L12">
-        <v>23.1</v>
+        <v>20.9</v>
+      </c>
+      <c r="M12">
+        <v>24.6</v>
       </c>
       <c r="R12" s="2">
         <v>25122</v>
@@ -947,13 +1016,13 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="E13">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="F13">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="H13">
         <v>19.6</v>
@@ -967,6 +1036,9 @@
       <c r="L13">
         <v>21.3</v>
       </c>
+      <c r="M13">
+        <v>23.3</v>
+      </c>
       <c r="R13" s="2">
         <v>25123</v>
       </c>
@@ -999,11 +1071,17 @@
       <c r="H14">
         <v>20</v>
       </c>
+      <c r="I14">
+        <v>25.5</v>
+      </c>
       <c r="J14">
         <v>24.9</v>
       </c>
       <c r="L14">
-        <v>21.5</v>
+        <v>19.8</v>
+      </c>
+      <c r="M14">
+        <v>20.5</v>
       </c>
       <c r="R14" s="2">
         <v>25124</v>
@@ -1037,11 +1115,17 @@
       <c r="H15">
         <v>18.8</v>
       </c>
+      <c r="I15">
+        <v>30.1</v>
+      </c>
       <c r="J15">
         <v>24.3</v>
       </c>
-      <c r="L15">
-        <v>22.2</v>
+      <c r="K15">
+        <v>16.5</v>
+      </c>
+      <c r="M15">
+        <v>22.4</v>
       </c>
       <c r="R15" s="2">
         <v>25125</v>
@@ -1063,6 +1147,15 @@
       <c r="C16">
         <v>15</v>
       </c>
+      <c r="D16">
+        <v>31.8</v>
+      </c>
+      <c r="E16">
+        <v>17.2</v>
+      </c>
+      <c r="F16">
+        <v>24.75</v>
+      </c>
       <c r="H16">
         <v>17.6</v>
       </c>
@@ -1070,13 +1163,13 @@
         <v>30.2</v>
       </c>
       <c r="J16">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="K16">
         <v>15.4</v>
       </c>
-      <c r="L16">
-        <v>20.6</v>
+      <c r="M16">
+        <v>19.5</v>
       </c>
       <c r="R16" s="2">
         <v>25126</v>
@@ -1111,13 +1204,19 @@
         <v>19.5</v>
       </c>
       <c r="I17">
-        <v>31.5</v>
+        <v>31.3</v>
+      </c>
+      <c r="J17">
+        <v>24.2</v>
       </c>
       <c r="K17">
         <v>18.4</v>
       </c>
       <c r="L17">
-        <v>24</v>
+        <v>24.3</v>
+      </c>
+      <c r="M17">
+        <v>20.9</v>
       </c>
       <c r="R17" s="2">
         <v>25127</v>
@@ -1154,11 +1253,17 @@
       <c r="I18">
         <v>24.4</v>
       </c>
+      <c r="J18">
+        <v>24.2</v>
+      </c>
       <c r="K18">
         <v>17.6</v>
       </c>
       <c r="L18">
-        <v>20.6</v>
+        <v>21.8</v>
+      </c>
+      <c r="M18">
+        <v>21.8</v>
       </c>
       <c r="R18" s="2">
         <v>25128</v>
@@ -1195,11 +1300,17 @@
       <c r="I19">
         <v>26</v>
       </c>
+      <c r="J19">
+        <v>23.2</v>
+      </c>
       <c r="K19">
         <v>18.8</v>
       </c>
       <c r="L19">
-        <v>21.6</v>
+        <v>19.7</v>
+      </c>
+      <c r="M19">
+        <v>20.8</v>
       </c>
       <c r="R19" s="2">
         <v>25129</v>
@@ -1236,11 +1347,17 @@
       <c r="I20">
         <v>28.2</v>
       </c>
+      <c r="J20">
+        <v>26</v>
+      </c>
       <c r="K20">
         <v>19.2</v>
       </c>
       <c r="L20">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="M20">
+        <v>22.7</v>
       </c>
       <c r="R20" s="2">
         <v>25130</v>
@@ -1263,10 +1380,10 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="E21">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="F21">
         <v>24.9</v>
@@ -1284,7 +1401,7 @@
         <v>19.2</v>
       </c>
       <c r="L21">
-        <v>23</v>
+        <v>20.8</v>
       </c>
       <c r="M21">
         <v>22</v>
@@ -1310,13 +1427,13 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>37.6</v>
+        <v>35.28</v>
       </c>
       <c r="E22">
         <v>20.2</v>
       </c>
       <c r="F22">
-        <v>28.9</v>
+        <v>27.7</v>
       </c>
       <c r="H22">
         <v>20.6</v>
@@ -1324,9 +1441,18 @@
       <c r="I22">
         <v>31</v>
       </c>
+      <c r="J22">
+        <v>28.2</v>
+      </c>
       <c r="K22">
         <v>19.3</v>
       </c>
+      <c r="L22">
+        <v>21.4</v>
+      </c>
+      <c r="M22">
+        <v>22</v>
+      </c>
       <c r="R22" s="2">
         <v>25132</v>
       </c>
@@ -1351,10 +1477,10 @@
         <v>33.6</v>
       </c>
       <c r="E23">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="F23">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="H23">
         <v>20.9</v>
@@ -1362,11 +1488,17 @@
       <c r="I23">
         <v>32.9</v>
       </c>
+      <c r="J23">
+        <v>25.8</v>
+      </c>
       <c r="K23">
         <v>18.8</v>
       </c>
       <c r="L23">
-        <v>20.4</v>
+        <v>23.9</v>
+      </c>
+      <c r="M23">
+        <v>22.8</v>
       </c>
       <c r="R23" s="2">
         <v>25133</v>
@@ -1403,12 +1535,18 @@
       <c r="I24">
         <v>26.1</v>
       </c>
+      <c r="J24">
+        <v>25.5</v>
+      </c>
       <c r="K24">
         <v>19</v>
       </c>
       <c r="L24">
         <v>22.1</v>
       </c>
+      <c r="M24">
+        <v>23.3</v>
+      </c>
       <c r="R24" s="2">
         <v>25134</v>
       </c>
@@ -1439,14 +1577,23 @@
         <v>22.6</v>
       </c>
       <c r="H25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I25">
         <v>22.6</v>
       </c>
+      <c r="J25">
+        <v>21.6</v>
+      </c>
       <c r="K25">
         <v>19.3</v>
       </c>
+      <c r="L25">
+        <v>20.6</v>
+      </c>
+      <c r="M25">
+        <v>20.3</v>
+      </c>
       <c r="R25" s="2">
         <v>25135</v>
       </c>
@@ -1482,12 +1629,18 @@
       <c r="I26">
         <v>27</v>
       </c>
+      <c r="J26">
+        <v>25</v>
+      </c>
       <c r="K26">
         <v>19.4</v>
       </c>
       <c r="L26">
         <v>21.6</v>
       </c>
+      <c r="M26">
+        <v>21</v>
+      </c>
       <c r="R26" s="2">
         <v>25136</v>
       </c>
@@ -1520,8 +1673,20 @@
       <c r="H27">
         <v>20.5</v>
       </c>
+      <c r="I27">
+        <v>30.4</v>
+      </c>
+      <c r="J27">
+        <v>26.8</v>
+      </c>
+      <c r="K27">
+        <v>19.5</v>
+      </c>
       <c r="L27">
-        <v>23.1</v>
+        <v>20.2</v>
+      </c>
+      <c r="M27">
+        <v>23.8</v>
       </c>
       <c r="R27" s="2">
         <v>25137</v>
@@ -1544,10 +1709,10 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="E28">
-        <v>19.6</v>
+        <v>20.2</v>
       </c>
       <c r="F28">
         <v>22.1</v>
@@ -1558,9 +1723,18 @@
       <c r="I28">
         <v>21</v>
       </c>
+      <c r="J28">
+        <v>21.3</v>
+      </c>
+      <c r="K28">
+        <v>19.1</v>
+      </c>
       <c r="L28">
         <v>19.2</v>
       </c>
+      <c r="M28">
+        <v>19.6</v>
+      </c>
       <c r="R28" s="2">
         <v>25138</v>
       </c>
@@ -1582,7 +1756,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="E29">
         <v>19.5</v>
@@ -1593,9 +1767,21 @@
       <c r="H29">
         <v>19.9</v>
       </c>
+      <c r="I29">
+        <v>28</v>
+      </c>
+      <c r="J29">
+        <v>24.6</v>
+      </c>
+      <c r="K29">
+        <v>18.7</v>
+      </c>
       <c r="L29">
         <v>21.6</v>
       </c>
+      <c r="M29">
+        <v>22.2</v>
+      </c>
       <c r="R29" s="2">
         <v>25139</v>
       </c>
@@ -1626,11 +1812,23 @@
         <v>24.9</v>
       </c>
       <c r="H30">
-        <v>17.2</v>
+        <v>17.8</v>
+      </c>
+      <c r="I30">
+        <v>30.8</v>
+      </c>
+      <c r="J30">
+        <v>27.5</v>
+      </c>
+      <c r="K30">
+        <v>16.1</v>
       </c>
       <c r="L30">
         <v>22.6</v>
       </c>
+      <c r="M30">
+        <v>23.8</v>
+      </c>
       <c r="R30" s="2">
         <v>25140</v>
       </c>
@@ -1663,9 +1861,21 @@
       <c r="H31">
         <v>19</v>
       </c>
+      <c r="I31">
+        <v>24.7</v>
+      </c>
+      <c r="J31">
+        <v>23</v>
+      </c>
+      <c r="K31">
+        <v>17.7</v>
+      </c>
       <c r="L31">
         <v>22.3</v>
       </c>
+      <c r="M31">
+        <v>22.4</v>
+      </c>
       <c r="R31" s="2">
         <v>25141</v>
       </c>
@@ -1698,8 +1908,20 @@
       <c r="H32">
         <v>19.4</v>
       </c>
+      <c r="I32">
+        <v>22.6</v>
+      </c>
+      <c r="J32">
+        <v>22.3</v>
+      </c>
+      <c r="K32">
+        <v>18.2</v>
+      </c>
       <c r="L32">
         <v>20.3</v>
+      </c>
+      <c r="M32">
+        <v>20.2</v>
       </c>
       <c r="R32" s="2">
         <v>25142</v>

--- a/results/04_final_refined_daily_hydroclimate_data/209/Daily_temperature_and_precipitation_station_209.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Daily_temperature_and_precipitation_station_209.xlsx
@@ -558,10 +558,10 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="E3">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="F3">
         <v>21.5</v>
@@ -673,7 +673,7 @@
         <v>16</v>
       </c>
       <c r="L5">
-        <v>23.9</v>
+        <v>20.8</v>
       </c>
       <c r="M5">
         <v>22</v>
@@ -810,6 +810,9 @@
       <c r="J8">
         <v>24.7</v>
       </c>
+      <c r="K8">
+        <v>19.3</v>
+      </c>
       <c r="L8">
         <v>24.5</v>
       </c>
@@ -854,6 +857,9 @@
       <c r="J9">
         <v>24.7</v>
       </c>
+      <c r="K9">
+        <v>18.8</v>
+      </c>
       <c r="L9">
         <v>25.5</v>
       </c>
@@ -931,7 +937,7 @@
         <v>29.5</v>
       </c>
       <c r="E11">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="F11">
         <v>24.9</v>
@@ -945,6 +951,9 @@
       <c r="J11">
         <v>24.5</v>
       </c>
+      <c r="K11">
+        <v>19.1</v>
+      </c>
       <c r="L11">
         <v>21</v>
       </c>
@@ -989,6 +998,9 @@
       <c r="J12">
         <v>26</v>
       </c>
+      <c r="K12">
+        <v>17.7</v>
+      </c>
       <c r="L12">
         <v>20.9</v>
       </c>
@@ -1033,6 +1045,9 @@
       <c r="J13">
         <v>25.8</v>
       </c>
+      <c r="K13">
+        <v>18.2</v>
+      </c>
       <c r="L13">
         <v>21.3</v>
       </c>
@@ -1077,6 +1092,9 @@
       <c r="J14">
         <v>24.9</v>
       </c>
+      <c r="K14">
+        <v>18.8</v>
+      </c>
       <c r="L14">
         <v>19.8</v>
       </c>
@@ -1124,8 +1142,11 @@
       <c r="K15">
         <v>16.5</v>
       </c>
+      <c r="L15">
+        <v>18.8</v>
+      </c>
       <c r="M15">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="R15" s="2">
         <v>25125</v>
@@ -1154,7 +1175,7 @@
         <v>17.2</v>
       </c>
       <c r="F16">
-        <v>24.75</v>
+        <v>24.5</v>
       </c>
       <c r="H16">
         <v>17.6</v>
@@ -1168,6 +1189,9 @@
       <c r="K16">
         <v>15.4</v>
       </c>
+      <c r="L16">
+        <v>20.6</v>
+      </c>
       <c r="M16">
         <v>19.5</v>
       </c>
@@ -1213,7 +1237,7 @@
         <v>18.4</v>
       </c>
       <c r="L17">
-        <v>24.3</v>
+        <v>21.7</v>
       </c>
       <c r="M17">
         <v>20.9</v>
@@ -1380,10 +1404,10 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="E21">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="F21">
         <v>24.9</v>
@@ -1427,13 +1451,16 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>35.28</v>
+        <v>32.8</v>
       </c>
       <c r="E22">
         <v>20.2</v>
       </c>
       <c r="F22">
-        <v>27.7</v>
+        <v>26.5</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
       </c>
       <c r="H22">
         <v>20.6</v>
@@ -1451,7 +1478,7 @@
         <v>21.4</v>
       </c>
       <c r="M22">
-        <v>22</v>
+        <v>23.7</v>
       </c>
       <c r="R22" s="2">
         <v>25132</v>
@@ -1474,13 +1501,16 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="E23">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="F23">
-        <v>26.8</v>
+        <v>26.7</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
       </c>
       <c r="H23">
         <v>20.9</v>
@@ -1498,7 +1528,7 @@
         <v>23.9</v>
       </c>
       <c r="M23">
-        <v>22.8</v>
+        <v>21.6</v>
       </c>
       <c r="R23" s="2">
         <v>25133</v>
@@ -1529,6 +1559,9 @@
       <c r="F24">
         <v>25.3</v>
       </c>
+      <c r="G24">
+        <v>1.2</v>
+      </c>
       <c r="H24">
         <v>20.4</v>
       </c>
@@ -1568,16 +1601,19 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="E25">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="F25">
-        <v>22.6</v>
+        <v>22.7</v>
+      </c>
+      <c r="G25">
+        <v>9</v>
       </c>
       <c r="H25">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I25">
         <v>22.6</v>
@@ -1623,6 +1659,9 @@
       <c r="F26">
         <v>24.3</v>
       </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
       <c r="H26">
         <v>20.6</v>
       </c>
@@ -1712,7 +1751,7 @@
         <v>24</v>
       </c>
       <c r="E28">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="F28">
         <v>22.1</v>
@@ -1759,7 +1798,7 @@
         <v>29.4</v>
       </c>
       <c r="E29">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="F29">
         <v>24.5</v>
@@ -1812,7 +1851,7 @@
         <v>24.9</v>
       </c>
       <c r="H30">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
       <c r="I30">
         <v>30.8</v>
@@ -1824,7 +1863,7 @@
         <v>16.1</v>
       </c>
       <c r="L30">
-        <v>22.6</v>
+        <v>19.2</v>
       </c>
       <c r="M30">
         <v>23.8</v>
@@ -1874,7 +1913,7 @@
         <v>22.3</v>
       </c>
       <c r="M31">
-        <v>22.4</v>
+        <v>21.4</v>
       </c>
       <c r="R31" s="2">
         <v>25141</v>

--- a/results/04_final_refined_daily_hydroclimate_data/209/Daily_temperature_and_precipitation_station_209.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Daily_temperature_and_precipitation_station_209.xlsx
@@ -999,7 +999,7 @@
         <v>26</v>
       </c>
       <c r="K12">
-        <v>17.7</v>
+        <v>16.9</v>
       </c>
       <c r="L12">
         <v>20.9</v>
@@ -1143,7 +1143,7 @@
         <v>16.5</v>
       </c>
       <c r="L15">
-        <v>18.8</v>
+        <v>22.2</v>
       </c>
       <c r="M15">
         <v>21.7</v>
@@ -1224,9 +1224,6 @@
       <c r="F17">
         <v>25.7</v>
       </c>
-      <c r="H17">
-        <v>19.5</v>
-      </c>
       <c r="I17">
         <v>31.3</v>
       </c>
@@ -1271,9 +1268,6 @@
       <c r="F18">
         <v>24.7</v>
       </c>
-      <c r="H18">
-        <v>19</v>
-      </c>
       <c r="I18">
         <v>24.4</v>
       </c>
@@ -1318,9 +1312,6 @@
       <c r="F19">
         <v>23.8</v>
       </c>
-      <c r="H19">
-        <v>20.2</v>
-      </c>
       <c r="I19">
         <v>26</v>
       </c>
@@ -1365,9 +1356,6 @@
       <c r="F20">
         <v>25</v>
       </c>
-      <c r="H20">
-        <v>20.6</v>
-      </c>
       <c r="I20">
         <v>28.2</v>
       </c>
@@ -1412,9 +1400,6 @@
       <c r="F21">
         <v>24.9</v>
       </c>
-      <c r="H21">
-        <v>20.3</v>
-      </c>
       <c r="I21">
         <v>28.6</v>
       </c>
@@ -1701,13 +1686,16 @@
         <v>26</v>
       </c>
       <c r="D27">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="E27">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="F27">
-        <v>25.6</v>
+        <v>25.7</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
       </c>
       <c r="H27">
         <v>20.5</v>
@@ -1718,9 +1706,6 @@
       <c r="J27">
         <v>26.8</v>
       </c>
-      <c r="K27">
-        <v>19.5</v>
-      </c>
       <c r="L27">
         <v>20.2</v>
       </c>
@@ -1748,13 +1733,16 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="E28">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="F28">
-        <v>22.1</v>
+        <v>22.21</v>
+      </c>
+      <c r="G28">
+        <v>4.9</v>
       </c>
       <c r="H28">
         <v>20.4</v>
@@ -1765,9 +1753,6 @@
       <c r="J28">
         <v>21.3</v>
       </c>
-      <c r="K28">
-        <v>19.1</v>
-      </c>
       <c r="L28">
         <v>19.2</v>
       </c>
@@ -1798,11 +1783,14 @@
         <v>29.4</v>
       </c>
       <c r="E29">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="F29">
         <v>24.5</v>
       </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
       <c r="H29">
         <v>19.9</v>
       </c>
@@ -1812,11 +1800,8 @@
       <c r="J29">
         <v>24.6</v>
       </c>
-      <c r="K29">
-        <v>18.7</v>
-      </c>
       <c r="L29">
-        <v>21.6</v>
+        <v>18.8</v>
       </c>
       <c r="M29">
         <v>22.2</v>
@@ -1850,6 +1835,9 @@
       <c r="F30">
         <v>24.9</v>
       </c>
+      <c r="G30">
+        <v>0.2</v>
+      </c>
       <c r="H30">
         <v>17.2</v>
       </c>
@@ -1859,9 +1847,6 @@
       <c r="J30">
         <v>27.5</v>
       </c>
-      <c r="K30">
-        <v>16.1</v>
-      </c>
       <c r="L30">
         <v>19.2</v>
       </c>
@@ -1897,6 +1882,9 @@
       <c r="F31">
         <v>25.3</v>
       </c>
+      <c r="G31">
+        <v>15.2</v>
+      </c>
       <c r="H31">
         <v>19</v>
       </c>
@@ -1906,14 +1894,11 @@
       <c r="J31">
         <v>23</v>
       </c>
-      <c r="K31">
-        <v>17.7</v>
-      </c>
       <c r="L31">
         <v>22.3</v>
       </c>
       <c r="M31">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="R31" s="2">
         <v>25141</v>
@@ -1939,10 +1924,13 @@
         <v>23.9</v>
       </c>
       <c r="E32">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="F32">
-        <v>21.4</v>
+        <v>21.5</v>
+      </c>
+      <c r="G32">
+        <v>9.699999999999999</v>
       </c>
       <c r="H32">
         <v>19.4</v>
@@ -1952,9 +1940,6 @@
       </c>
       <c r="J32">
         <v>22.3</v>
-      </c>
-      <c r="K32">
-        <v>18.2</v>
       </c>
       <c r="L32">
         <v>20.3</v>

--- a/results/04_final_refined_daily_hydroclimate_data/209/Daily_temperature_and_precipitation_station_209.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Daily_temperature_and_precipitation_station_209.xlsx
@@ -989,6 +989,9 @@
       <c r="F12">
         <v>24.9</v>
       </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
       <c r="H12">
         <v>19.2</v>
       </c>
@@ -1036,6 +1039,9 @@
       <c r="F13">
         <v>25.5</v>
       </c>
+      <c r="G13">
+        <v>21.5</v>
+      </c>
       <c r="H13">
         <v>19.6</v>
       </c>
@@ -1083,6 +1089,9 @@
       <c r="F14">
         <v>23.5</v>
       </c>
+      <c r="G14">
+        <v>24</v>
+      </c>
       <c r="H14">
         <v>20</v>
       </c>
@@ -1130,6 +1139,9 @@
       <c r="F15">
         <v>24.6</v>
       </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
       <c r="H15">
         <v>18.8</v>
       </c>
@@ -1177,6 +1189,9 @@
       <c r="F16">
         <v>24.5</v>
       </c>
+      <c r="G16">
+        <v>3.7</v>
+      </c>
       <c r="H16">
         <v>17.6</v>
       </c>
@@ -1224,6 +1239,12 @@
       <c r="F17">
         <v>25.7</v>
       </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>19.5</v>
+      </c>
       <c r="I17">
         <v>31.3</v>
       </c>
@@ -1268,6 +1289,12 @@
       <c r="F18">
         <v>24.7</v>
       </c>
+      <c r="G18">
+        <v>0.3</v>
+      </c>
+      <c r="H18">
+        <v>19</v>
+      </c>
       <c r="I18">
         <v>24.4</v>
       </c>
@@ -1312,6 +1339,12 @@
       <c r="F19">
         <v>23.8</v>
       </c>
+      <c r="G19">
+        <v>5.3</v>
+      </c>
+      <c r="H19">
+        <v>20.2</v>
+      </c>
       <c r="I19">
         <v>26</v>
       </c>
@@ -1356,6 +1389,12 @@
       <c r="F20">
         <v>25</v>
       </c>
+      <c r="G20">
+        <v>19.6</v>
+      </c>
+      <c r="H20">
+        <v>20.6</v>
+      </c>
       <c r="I20">
         <v>28.2</v>
       </c>
@@ -1400,6 +1439,12 @@
       <c r="F21">
         <v>24.9</v>
       </c>
+      <c r="G21">
+        <v>0.2</v>
+      </c>
+      <c r="H21">
+        <v>20.3</v>
+      </c>
       <c r="I21">
         <v>28.6</v>
       </c>
@@ -1457,13 +1502,13 @@
         <v>28.2</v>
       </c>
       <c r="K22">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="L22">
         <v>21.4</v>
       </c>
       <c r="M22">
-        <v>23.7</v>
+        <v>22</v>
       </c>
       <c r="R22" s="2">
         <v>25132</v>
@@ -1607,7 +1652,7 @@
         <v>21.6</v>
       </c>
       <c r="K25">
-        <v>19.3</v>
+        <v>18.5</v>
       </c>
       <c r="L25">
         <v>20.6</v>
@@ -1706,6 +1751,9 @@
       <c r="J27">
         <v>26.8</v>
       </c>
+      <c r="K27">
+        <v>19.5</v>
+      </c>
       <c r="L27">
         <v>20.2</v>
       </c>
@@ -1739,7 +1787,7 @@
         <v>20.2</v>
       </c>
       <c r="F28">
-        <v>22.21</v>
+        <v>22.1</v>
       </c>
       <c r="G28">
         <v>4.9</v>
@@ -1753,6 +1801,9 @@
       <c r="J28">
         <v>21.3</v>
       </c>
+      <c r="K28">
+        <v>19.1</v>
+      </c>
       <c r="L28">
         <v>19.2</v>
       </c>
@@ -1780,7 +1831,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="E29">
         <v>19.5</v>
@@ -1800,8 +1851,11 @@
       <c r="J29">
         <v>24.6</v>
       </c>
+      <c r="K29">
+        <v>18.7</v>
+      </c>
       <c r="L29">
-        <v>18.8</v>
+        <v>21.6</v>
       </c>
       <c r="M29">
         <v>22.2</v>
@@ -1847,6 +1901,9 @@
       <c r="J30">
         <v>27.5</v>
       </c>
+      <c r="K30">
+        <v>16.1</v>
+      </c>
       <c r="L30">
         <v>19.2</v>
       </c>
@@ -1894,6 +1951,9 @@
       <c r="J31">
         <v>23</v>
       </c>
+      <c r="K31">
+        <v>17.7</v>
+      </c>
       <c r="L31">
         <v>22.3</v>
       </c>
@@ -1940,6 +2000,9 @@
       </c>
       <c r="J32">
         <v>22.3</v>
+      </c>
+      <c r="K32">
+        <v>18.2</v>
       </c>
       <c r="L32">
         <v>20.3</v>

--- a/results/04_final_refined_daily_hydroclimate_data/209/Daily_temperature_and_precipitation_station_209.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Daily_temperature_and_precipitation_station_209.xlsx
@@ -529,10 +529,10 @@
         <v>27.7</v>
       </c>
       <c r="K2">
-        <v>15.4</v>
+        <v>16.2</v>
       </c>
       <c r="L2">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="M2">
         <v>24</v>
@@ -579,10 +579,10 @@
         <v>18</v>
       </c>
       <c r="L3">
-        <v>18.4</v>
+        <v>19.1</v>
       </c>
       <c r="M3">
-        <v>22.7</v>
+        <v>18.9</v>
       </c>
       <c r="R3" s="2">
         <v>25113</v>
@@ -623,13 +623,13 @@
         <v>20.6</v>
       </c>
       <c r="K4">
-        <v>18.4</v>
+        <v>19</v>
       </c>
       <c r="L4">
-        <v>21.7</v>
+        <v>23.9</v>
       </c>
       <c r="M4">
-        <v>18.1</v>
+        <v>23.2</v>
       </c>
       <c r="R4" s="2">
         <v>25114</v>
@@ -673,10 +673,10 @@
         <v>16</v>
       </c>
       <c r="L5">
-        <v>20.8</v>
+        <v>23.9</v>
       </c>
       <c r="M5">
-        <v>22</v>
+        <v>24.1</v>
       </c>
       <c r="R5" s="2">
         <v>25115</v>
@@ -720,7 +720,7 @@
         <v>18.6</v>
       </c>
       <c r="L6">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="M6">
         <v>22.8</v>
@@ -764,7 +764,7 @@
         <v>25</v>
       </c>
       <c r="K7">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="L7">
         <v>25.8</v>
@@ -814,7 +814,7 @@
         <v>19.3</v>
       </c>
       <c r="L8">
-        <v>24.5</v>
+        <v>25.2</v>
       </c>
       <c r="M8">
         <v>24.4</v>
@@ -861,7 +861,7 @@
         <v>18.8</v>
       </c>
       <c r="L9">
-        <v>25.5</v>
+        <v>26.3</v>
       </c>
       <c r="M9">
         <v>23.8</v>
@@ -905,13 +905,13 @@
         <v>21.9</v>
       </c>
       <c r="K10">
-        <v>18.1</v>
+        <v>18.7</v>
       </c>
       <c r="L10">
-        <v>19.2</v>
+        <v>22.6</v>
       </c>
       <c r="M10">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="R10" s="2">
         <v>25120</v>
@@ -955,7 +955,7 @@
         <v>19.1</v>
       </c>
       <c r="L11">
-        <v>21</v>
+        <v>23.1</v>
       </c>
       <c r="M11">
         <v>21.1</v>
@@ -1002,13 +1002,13 @@
         <v>26</v>
       </c>
       <c r="K12">
-        <v>16.9</v>
+        <v>17.7</v>
       </c>
       <c r="L12">
-        <v>20.9</v>
+        <v>23.1</v>
       </c>
       <c r="M12">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="R12" s="2">
         <v>25122</v>
@@ -1055,7 +1055,7 @@
         <v>18.2</v>
       </c>
       <c r="L13">
-        <v>21.3</v>
+        <v>24.2</v>
       </c>
       <c r="M13">
         <v>23.3</v>
@@ -1105,7 +1105,7 @@
         <v>18.8</v>
       </c>
       <c r="L14">
-        <v>19.8</v>
+        <v>21.5</v>
       </c>
       <c r="M14">
         <v>20.5</v>
@@ -1152,13 +1152,13 @@
         <v>24.3</v>
       </c>
       <c r="K15">
-        <v>16.5</v>
+        <v>17.3</v>
       </c>
       <c r="L15">
         <v>22.2</v>
       </c>
       <c r="M15">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="R15" s="2">
         <v>25125</v>
@@ -1202,10 +1202,10 @@
         <v>21.2</v>
       </c>
       <c r="K16">
-        <v>15.4</v>
+        <v>16.2</v>
       </c>
       <c r="L16">
-        <v>20.6</v>
+        <v>23.3</v>
       </c>
       <c r="M16">
         <v>19.5</v>
@@ -1255,7 +1255,7 @@
         <v>18.4</v>
       </c>
       <c r="L17">
-        <v>21.7</v>
+        <v>24.3</v>
       </c>
       <c r="M17">
         <v>20.9</v>
@@ -1355,7 +1355,7 @@
         <v>18.8</v>
       </c>
       <c r="L19">
-        <v>19.7</v>
+        <v>21.6</v>
       </c>
       <c r="M19">
         <v>20.8</v>
@@ -1405,10 +1405,10 @@
         <v>19.2</v>
       </c>
       <c r="L20">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M20">
-        <v>22.7</v>
+        <v>23.6</v>
       </c>
       <c r="R20" s="2">
         <v>25130</v>
@@ -1455,10 +1455,10 @@
         <v>19.2</v>
       </c>
       <c r="L21">
-        <v>20.8</v>
+        <v>23</v>
       </c>
       <c r="M21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R21" s="2">
         <v>25131</v>
@@ -1505,10 +1505,10 @@
         <v>19.5</v>
       </c>
       <c r="L22">
-        <v>21.4</v>
+        <v>24</v>
       </c>
       <c r="M22">
-        <v>22</v>
+        <v>23.7</v>
       </c>
       <c r="R22" s="2">
         <v>25132</v>
@@ -1552,13 +1552,13 @@
         <v>25.8</v>
       </c>
       <c r="K23">
-        <v>18.8</v>
+        <v>19.5</v>
       </c>
       <c r="L23">
         <v>23.9</v>
       </c>
       <c r="M23">
-        <v>21.6</v>
+        <v>22.8</v>
       </c>
       <c r="R23" s="2">
         <v>25133</v>
@@ -1605,7 +1605,7 @@
         <v>19</v>
       </c>
       <c r="L24">
-        <v>22.1</v>
+        <v>23.2</v>
       </c>
       <c r="M24">
         <v>23.3</v>
@@ -1652,10 +1652,10 @@
         <v>21.6</v>
       </c>
       <c r="K25">
-        <v>18.5</v>
+        <v>19.3</v>
       </c>
       <c r="L25">
-        <v>20.6</v>
+        <v>21.2</v>
       </c>
       <c r="M25">
         <v>20.3</v>
@@ -1705,10 +1705,10 @@
         <v>19.4</v>
       </c>
       <c r="L26">
-        <v>21.6</v>
+        <v>23.1</v>
       </c>
       <c r="M26">
-        <v>21</v>
+        <v>22.1</v>
       </c>
       <c r="R26" s="2">
         <v>25136</v>
@@ -1755,7 +1755,7 @@
         <v>19.5</v>
       </c>
       <c r="L27">
-        <v>20.2</v>
+        <v>23.1</v>
       </c>
       <c r="M27">
         <v>23.8</v>
@@ -1805,7 +1805,7 @@
         <v>19.1</v>
       </c>
       <c r="L28">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="M28">
         <v>19.6</v>
@@ -1905,7 +1905,7 @@
         <v>16.1</v>
       </c>
       <c r="L30">
-        <v>19.2</v>
+        <v>22.6</v>
       </c>
       <c r="M30">
         <v>23.8</v>
